--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5251-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5251-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E09A05A-8AF6-4C88-975B-608AAE342D37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86FD2723-F7D4-48E9-8ED9-CF96359662E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8486B9CC-D015-45AB-BA99-F88604447C54}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{770D805B-4017-40C6-A49A-B9252E3F40EE}"/>
   </bookViews>
   <sheets>
     <sheet name="5251-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1433,27 +1433,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5248A48-612F-478C-9A3F-AD6B4E36A8EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A03A8E-78AB-49B7-A29B-8C0243331B08}">
   <dimension ref="A1:X20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="6.25" customWidth="1"/>
-    <col min="15" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1486,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1523,7 +1522,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1575,7 +1574,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1643,7 +1642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1715,7 +1714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1787,7 +1786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="34">
         <v>2022</v>
       </c>
@@ -1859,7 +1858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2021</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2020</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2019</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2018</v>
       </c>
@@ -2147,7 +2146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2017</v>
       </c>
@@ -2219,7 +2218,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2016</v>
       </c>
@@ -2291,7 +2290,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2015</v>
       </c>
@@ -2363,7 +2362,7 @@
         <v>7.48</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2014</v>
       </c>
@@ -2435,7 +2434,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2013</v>
       </c>
@@ -2507,7 +2506,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2012</v>
       </c>
@@ -2579,7 +2578,7 @@
         <v>7.65</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2011</v>
       </c>
@@ -2651,7 +2650,7 @@
         <v>5.96</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2010</v>
       </c>
@@ -2723,7 +2722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36" t="s">
         <v>36</v>
       </c>
